--- a/data/lossofsale_sg_edappally.xlsx
+++ b/data/lossofsale_sg_edappally.xlsx
@@ -1349,20 +1349,20 @@
       </c>
       <c t="inlineStr" r="C23">
         <is>
-          <t xml:space="preserve">Nithin</t>
+          <t xml:space="preserve">melvin</t>
         </is>
       </c>
       <c r="D23" s="65">
-        <v>9188031437</v>
+        <v>9895578570</v>
       </c>
       <c t="inlineStr" r="E23">
         <is>
-          <t xml:space="preserve">26-01-2026</t>
+          <t xml:space="preserve">29-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F23">
         <is>
-          <t xml:space="preserve">RAMITH K</t>
+          <t xml:space="preserve">ABIN KRISHNA S</t>
         </is>
       </c>
       <c t="inlineStr" r="G23">
@@ -1387,7 +1387,7 @@
       </c>
       <c t="inlineStr" r="K23">
         <is>
-          <t xml:space="preserve">Loss</t>
+          <t xml:space="preserve">..</t>
         </is>
       </c>
     </row>
@@ -1397,25 +1397,25 @@
       </c>
       <c t="inlineStr" r="B24">
         <is>
-          <t xml:space="preserve">14-12-2025</t>
+          <t xml:space="preserve">15-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C24">
         <is>
-          <t xml:space="preserve">melvin</t>
+          <t xml:space="preserve">Tojin</t>
         </is>
       </c>
       <c r="D24" s="65">
-        <v>9895578570</v>
+        <v>8943034163</v>
       </c>
       <c t="inlineStr" r="E24">
         <is>
-          <t xml:space="preserve">29-12-2025</t>
+          <t xml:space="preserve">10-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F24">
         <is>
-          <t xml:space="preserve">ABIN KRISHNA S</t>
+          <t xml:space="preserve">Althaf A</t>
         </is>
       </c>
       <c t="inlineStr" r="G24">
@@ -1425,22 +1425,17 @@
       </c>
       <c t="inlineStr" r="H24">
         <is>
-          <t xml:space="preserve">ENQUIRY</t>
+          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
         </is>
       </c>
       <c t="inlineStr" r="I24">
         <is>
-          <t xml:space="preserve">Enquiry for Relative/Friend</t>
+          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
         </is>
       </c>
       <c t="inlineStr" r="J24">
         <is>
           <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="K24">
-        <is>
-          <t xml:space="preserve">..</t>
         </is>
       </c>
     </row>
@@ -1455,20 +1450,20 @@
       </c>
       <c t="inlineStr" r="C25">
         <is>
-          <t xml:space="preserve">Tojin</t>
+          <t xml:space="preserve">anush</t>
         </is>
       </c>
       <c r="D25" s="65">
-        <v>8943034163</v>
+        <v>8086462505</v>
       </c>
       <c t="inlineStr" r="E25">
         <is>
-          <t xml:space="preserve">10-01-2026</t>
+          <t xml:space="preserve">18-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F25">
         <is>
-          <t xml:space="preserve">Althaf A</t>
+          <t xml:space="preserve">AKSHAYDAS.M</t>
         </is>
       </c>
       <c t="inlineStr" r="G25">
@@ -1478,17 +1473,22 @@
       </c>
       <c t="inlineStr" r="H25">
         <is>
-          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
+          <t xml:space="preserve">PRODUCT</t>
         </is>
       </c>
       <c t="inlineStr" r="I25">
         <is>
-          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
+          <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
         </is>
       </c>
       <c t="inlineStr" r="J25">
         <is>
           <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K25">
+        <is>
+          <t xml:space="preserve">kurutha</t>
         </is>
       </c>
     </row>
@@ -1498,25 +1498,25 @@
       </c>
       <c t="inlineStr" r="B26">
         <is>
-          <t xml:space="preserve">15-12-2025</t>
+          <t xml:space="preserve">16-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C26">
         <is>
-          <t xml:space="preserve">anush</t>
+          <t xml:space="preserve">Abraham</t>
         </is>
       </c>
       <c r="D26" s="65">
-        <v>8086462505</v>
+        <v>9747793966</v>
       </c>
       <c t="inlineStr" r="E26">
         <is>
-          <t xml:space="preserve">18-01-2026</t>
+          <t xml:space="preserve">10-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F26">
         <is>
-          <t xml:space="preserve">AKSHAYDAS.M</t>
+          <t xml:space="preserve">Althaf A</t>
         </is>
       </c>
       <c t="inlineStr" r="G26">
@@ -1526,12 +1526,12 @@
       </c>
       <c t="inlineStr" r="H26">
         <is>
-          <t xml:space="preserve">PRODUCT</t>
+          <t xml:space="preserve">PRICING</t>
         </is>
       </c>
       <c t="inlineStr" r="I26">
         <is>
-          <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
+          <t xml:space="preserve">RENT TO HIGH</t>
         </is>
       </c>
       <c t="inlineStr" r="J26">
@@ -1541,7 +1541,7 @@
       </c>
       <c t="inlineStr" r="K26">
         <is>
-          <t xml:space="preserve">kurutha</t>
+          <t xml:space="preserve">.</t>
         </is>
       </c>
     </row>
@@ -1556,15 +1556,15 @@
       </c>
       <c t="inlineStr" r="C27">
         <is>
-          <t xml:space="preserve">Abraham</t>
+          <t xml:space="preserve">Ashik</t>
         </is>
       </c>
       <c r="D27" s="65">
-        <v>9747793966</v>
+        <v>9037260665</v>
       </c>
       <c t="inlineStr" r="E27">
         <is>
-          <t xml:space="preserve">10-01-2026</t>
+          <t xml:space="preserve">22-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F27">
@@ -1579,12 +1579,12 @@
       </c>
       <c t="inlineStr" r="H27">
         <is>
-          <t xml:space="preserve">PRICING</t>
+          <t xml:space="preserve">PRODUCT</t>
         </is>
       </c>
       <c t="inlineStr" r="I27">
         <is>
-          <t xml:space="preserve">RENT TO HIGH</t>
+          <t xml:space="preserve">REQUIRED DESIGN NOT AVAILABLE</t>
         </is>
       </c>
       <c t="inlineStr" r="J27">
@@ -1609,20 +1609,20 @@
       </c>
       <c t="inlineStr" r="C28">
         <is>
-          <t xml:space="preserve">Ashik</t>
+          <t xml:space="preserve">sandeep</t>
         </is>
       </c>
       <c r="D28" s="65">
-        <v>9037260665</v>
+        <v>9947153224</v>
       </c>
       <c t="inlineStr" r="E28">
         <is>
-          <t xml:space="preserve">22-12-2025</t>
+          <t xml:space="preserve">16-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F28">
         <is>
-          <t xml:space="preserve">Althaf A</t>
+          <t xml:space="preserve">Nithin binoy</t>
         </is>
       </c>
       <c t="inlineStr" r="G28">
@@ -1632,12 +1632,12 @@
       </c>
       <c t="inlineStr" r="H28">
         <is>
-          <t xml:space="preserve">PRODUCT</t>
+          <t xml:space="preserve">ENQUIRY</t>
         </is>
       </c>
       <c t="inlineStr" r="I28">
         <is>
-          <t xml:space="preserve">REQUIRED DESIGN NOT AVAILABLE</t>
+          <t xml:space="preserve">Enquiry for Relative/Friend</t>
         </is>
       </c>
       <c t="inlineStr" r="J28">
@@ -1647,7 +1647,7 @@
       </c>
       <c t="inlineStr" r="K28">
         <is>
-          <t xml:space="preserve">.</t>
+          <t xml:space="preserve">loos</t>
         </is>
       </c>
     </row>
@@ -1657,25 +1657,25 @@
       </c>
       <c t="inlineStr" r="B29">
         <is>
-          <t xml:space="preserve">16-12-2025</t>
+          <t xml:space="preserve">17-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C29">
         <is>
-          <t xml:space="preserve">sandeep</t>
+          <t xml:space="preserve">Jebin</t>
         </is>
       </c>
       <c r="D29" s="65">
-        <v>9947153224</v>
+        <v>8124004551</v>
       </c>
       <c t="inlineStr" r="E29">
         <is>
-          <t xml:space="preserve">16-12-2025</t>
+          <t xml:space="preserve">14-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F29">
         <is>
-          <t xml:space="preserve">Nithin binoy</t>
+          <t xml:space="preserve">Althaf A</t>
         </is>
       </c>
       <c t="inlineStr" r="G29">
@@ -1685,12 +1685,12 @@
       </c>
       <c t="inlineStr" r="H29">
         <is>
-          <t xml:space="preserve">ENQUIRY</t>
+          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
         </is>
       </c>
       <c t="inlineStr" r="I29">
         <is>
-          <t xml:space="preserve">Enquiry for Relative/Friend</t>
+          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
         </is>
       </c>
       <c t="inlineStr" r="J29">
@@ -1700,7 +1700,7 @@
       </c>
       <c t="inlineStr" r="K29">
         <is>
-          <t xml:space="preserve">loos</t>
+          <t xml:space="preserve">they will come sunday</t>
         </is>
       </c>
     </row>
@@ -1715,20 +1715,20 @@
       </c>
       <c t="inlineStr" r="C30">
         <is>
-          <t xml:space="preserve">Jebin</t>
+          <t xml:space="preserve">benadict</t>
         </is>
       </c>
       <c r="D30" s="65">
-        <v>8124004551</v>
+        <v>9562474208</v>
       </c>
       <c t="inlineStr" r="E30">
         <is>
-          <t xml:space="preserve">14-01-2026</t>
+          <t xml:space="preserve">17-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F30">
         <is>
-          <t xml:space="preserve">Althaf A</t>
+          <t xml:space="preserve">Nithin binoy</t>
         </is>
       </c>
       <c t="inlineStr" r="G30">
@@ -1738,12 +1738,12 @@
       </c>
       <c t="inlineStr" r="H30">
         <is>
-          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
+          <t xml:space="preserve">PRODUCT</t>
         </is>
       </c>
       <c t="inlineStr" r="I30">
         <is>
-          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
+          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
         </is>
       </c>
       <c t="inlineStr" r="J30">
@@ -1753,7 +1753,7 @@
       </c>
       <c t="inlineStr" r="K30">
         <is>
-          <t xml:space="preserve">they will come sunday</t>
+          <t xml:space="preserve">loss</t>
         </is>
       </c>
     </row>
@@ -1768,20 +1768,20 @@
       </c>
       <c t="inlineStr" r="C31">
         <is>
-          <t xml:space="preserve">benadict</t>
+          <t xml:space="preserve">toy</t>
         </is>
       </c>
       <c r="D31" s="65">
-        <v>9562474208</v>
+        <v>9846105212</v>
       </c>
       <c t="inlineStr" r="E31">
         <is>
-          <t xml:space="preserve">17-12-2025</t>
+          <t xml:space="preserve">28-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F31">
         <is>
-          <t xml:space="preserve">Nithin binoy</t>
+          <t xml:space="preserve">SWAROOP S K</t>
         </is>
       </c>
       <c t="inlineStr" r="G31">
@@ -1791,12 +1791,12 @@
       </c>
       <c t="inlineStr" r="H31">
         <is>
-          <t xml:space="preserve">PRODUCT</t>
+          <t xml:space="preserve">SIZE NOT SUITABLE</t>
         </is>
       </c>
       <c t="inlineStr" r="I31">
         <is>
-          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
+          <t xml:space="preserve">SIZE TOO SMALL</t>
         </is>
       </c>
       <c t="inlineStr" r="J31">
@@ -1806,7 +1806,7 @@
       </c>
       <c t="inlineStr" r="K31">
         <is>
-          <t xml:space="preserve">loss</t>
+          <t xml:space="preserve">.</t>
         </is>
       </c>
     </row>
@@ -1821,20 +1821,20 @@
       </c>
       <c t="inlineStr" r="C32">
         <is>
-          <t xml:space="preserve">toy</t>
+          <t xml:space="preserve">suhail</t>
         </is>
       </c>
       <c r="D32" s="65">
-        <v>9846105212</v>
+        <v>8137912784</v>
       </c>
       <c t="inlineStr" r="E32">
         <is>
-          <t xml:space="preserve">28-12-2025</t>
+          <t xml:space="preserve">17-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F32">
         <is>
-          <t xml:space="preserve">SWAROOP S K</t>
+          <t xml:space="preserve">Mohamed Farseen C S</t>
         </is>
       </c>
       <c t="inlineStr" r="G32">
@@ -1844,12 +1844,12 @@
       </c>
       <c t="inlineStr" r="H32">
         <is>
-          <t xml:space="preserve">SIZE NOT SUITABLE</t>
+          <t xml:space="preserve">ENQUIRY</t>
         </is>
       </c>
       <c t="inlineStr" r="I32">
         <is>
-          <t xml:space="preserve">SIZE TOO SMALL</t>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
         </is>
       </c>
       <c t="inlineStr" r="J32">
@@ -1859,7 +1859,7 @@
       </c>
       <c t="inlineStr" r="K32">
         <is>
-          <t xml:space="preserve">.</t>
+          <t xml:space="preserve">enquiry</t>
         </is>
       </c>
     </row>
@@ -1874,11 +1874,11 @@
       </c>
       <c t="inlineStr" r="C33">
         <is>
-          <t xml:space="preserve">suhail</t>
+          <t xml:space="preserve">althaf</t>
         </is>
       </c>
       <c r="D33" s="65">
-        <v>8137912784</v>
+        <v>7306166226</v>
       </c>
       <c t="inlineStr" r="E33">
         <is>
@@ -1887,7 +1887,7 @@
       </c>
       <c t="inlineStr" r="F33">
         <is>
-          <t xml:space="preserve">Mohamed Farseen C S</t>
+          <t xml:space="preserve">Nithin binoy</t>
         </is>
       </c>
       <c t="inlineStr" r="G33">
@@ -1897,12 +1897,12 @@
       </c>
       <c t="inlineStr" r="H33">
         <is>
-          <t xml:space="preserve">ENQUIRY</t>
+          <t xml:space="preserve">PRODUCT</t>
         </is>
       </c>
       <c t="inlineStr" r="I33">
         <is>
-          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
         </is>
       </c>
       <c t="inlineStr" r="J33">
@@ -1912,7 +1912,7 @@
       </c>
       <c t="inlineStr" r="K33">
         <is>
-          <t xml:space="preserve">enquiry</t>
+          <t xml:space="preserve">loss</t>
         </is>
       </c>
     </row>
@@ -1927,20 +1927,20 @@
       </c>
       <c t="inlineStr" r="C34">
         <is>
-          <t xml:space="preserve">althaf</t>
+          <t xml:space="preserve">naveen</t>
         </is>
       </c>
       <c r="D34" s="65">
-        <v>7306166226</v>
+        <v>8281044850</v>
       </c>
       <c t="inlineStr" r="E34">
         <is>
-          <t xml:space="preserve">17-12-2025</t>
+          <t xml:space="preserve">08-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F34">
         <is>
-          <t xml:space="preserve">Nithin binoy</t>
+          <t xml:space="preserve">ABIN KRISHNA S</t>
         </is>
       </c>
       <c t="inlineStr" r="G34">
@@ -1965,7 +1965,7 @@
       </c>
       <c t="inlineStr" r="K34">
         <is>
-          <t xml:space="preserve">loss</t>
+          <t xml:space="preserve">..</t>
         </is>
       </c>
     </row>
@@ -1975,25 +1975,25 @@
       </c>
       <c t="inlineStr" r="B35">
         <is>
-          <t xml:space="preserve">17-12-2025</t>
+          <t xml:space="preserve">18-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C35">
         <is>
-          <t xml:space="preserve">naveen</t>
+          <t xml:space="preserve">Umar</t>
         </is>
       </c>
       <c r="D35" s="65">
-        <v>8281044850</v>
+        <v>9447767211</v>
       </c>
       <c t="inlineStr" r="E35">
         <is>
-          <t xml:space="preserve">08-01-2026</t>
+          <t xml:space="preserve">31-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F35">
         <is>
-          <t xml:space="preserve">ABIN KRISHNA S</t>
+          <t xml:space="preserve">Althaf A</t>
         </is>
       </c>
       <c t="inlineStr" r="G35">
@@ -2003,12 +2003,12 @@
       </c>
       <c t="inlineStr" r="H35">
         <is>
-          <t xml:space="preserve">PRODUCT</t>
+          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
         </is>
       </c>
       <c t="inlineStr" r="I35">
         <is>
-          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
+          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
         </is>
       </c>
       <c t="inlineStr" r="J35">
@@ -2018,7 +2018,7 @@
       </c>
       <c t="inlineStr" r="K35">
         <is>
-          <t xml:space="preserve">..</t>
+          <t xml:space="preserve">family dissaproval they bought new one instead of rental</t>
         </is>
       </c>
     </row>
@@ -2033,20 +2033,20 @@
       </c>
       <c t="inlineStr" r="C36">
         <is>
-          <t xml:space="preserve">Umar</t>
+          <t xml:space="preserve">vishnu</t>
         </is>
       </c>
       <c r="D36" s="65">
-        <v>9447767211</v>
+        <v>8281533975</v>
       </c>
       <c t="inlineStr" r="E36">
         <is>
-          <t xml:space="preserve">31-12-2025</t>
+          <t xml:space="preserve">18-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F36">
         <is>
-          <t xml:space="preserve">Althaf A</t>
+          <t xml:space="preserve">Mohamed Farseen C S</t>
         </is>
       </c>
       <c t="inlineStr" r="G36">
@@ -2071,7 +2071,7 @@
       </c>
       <c t="inlineStr" r="K36">
         <is>
-          <t xml:space="preserve">family dissaproval they bought new one instead of rental</t>
+          <t xml:space="preserve">family disapproved entire model in our store</t>
         </is>
       </c>
     </row>
@@ -2086,11 +2086,11 @@
       </c>
       <c t="inlineStr" r="C37">
         <is>
-          <t xml:space="preserve">vishnu</t>
+          <t xml:space="preserve">abin</t>
         </is>
       </c>
       <c r="D37" s="65">
-        <v>8281533975</v>
+        <v>9895568883</v>
       </c>
       <c t="inlineStr" r="E37">
         <is>
@@ -2099,7 +2099,7 @@
       </c>
       <c t="inlineStr" r="F37">
         <is>
-          <t xml:space="preserve">Mohamed Farseen C S</t>
+          <t xml:space="preserve">Nithin binoy</t>
         </is>
       </c>
       <c t="inlineStr" r="G37">
@@ -2109,12 +2109,12 @@
       </c>
       <c t="inlineStr" r="H37">
         <is>
-          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
+          <t xml:space="preserve">ENQUIRY</t>
         </is>
       </c>
       <c t="inlineStr" r="I37">
         <is>
-          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
+          <t xml:space="preserve">SHOE</t>
         </is>
       </c>
       <c t="inlineStr" r="J37">
@@ -2124,7 +2124,7 @@
       </c>
       <c t="inlineStr" r="K37">
         <is>
-          <t xml:space="preserve">family disapproved entire model in our store</t>
+          <t xml:space="preserve">size not available 10 or 9 black glossy</t>
         </is>
       </c>
     </row>
@@ -2139,20 +2139,20 @@
       </c>
       <c t="inlineStr" r="C38">
         <is>
-          <t xml:space="preserve">abin</t>
+          <t xml:space="preserve">Gokul</t>
         </is>
       </c>
       <c r="D38" s="65">
-        <v>9895568883</v>
+        <v>8129932346</v>
       </c>
       <c t="inlineStr" r="E38">
         <is>
-          <t xml:space="preserve">18-12-2025</t>
+          <t xml:space="preserve">11-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F38">
         <is>
-          <t xml:space="preserve">Nithin binoy</t>
+          <t xml:space="preserve">Althaf A</t>
         </is>
       </c>
       <c t="inlineStr" r="G38">
@@ -2167,7 +2167,7 @@
       </c>
       <c t="inlineStr" r="I38">
         <is>
-          <t xml:space="preserve">SHOE</t>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
         </is>
       </c>
       <c t="inlineStr" r="J38">
@@ -2177,7 +2177,7 @@
       </c>
       <c t="inlineStr" r="K38">
         <is>
-          <t xml:space="preserve">size not available 10 or 9 black glossy</t>
+          <t xml:space="preserve">internal issues</t>
         </is>
       </c>
     </row>
@@ -2192,15 +2192,15 @@
       </c>
       <c t="inlineStr" r="C39">
         <is>
-          <t xml:space="preserve">Gokul</t>
+          <t xml:space="preserve">Amal</t>
         </is>
       </c>
       <c r="D39" s="65">
-        <v>8129932346</v>
+        <v>8921643216</v>
       </c>
       <c t="inlineStr" r="E39">
         <is>
-          <t xml:space="preserve">11-01-2026</t>
+          <t xml:space="preserve">18-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F39">
@@ -2215,12 +2215,12 @@
       </c>
       <c t="inlineStr" r="H39">
         <is>
-          <t xml:space="preserve">ENQUIRY</t>
+          <t xml:space="preserve">PRODUCT</t>
         </is>
       </c>
       <c t="inlineStr" r="I39">
         <is>
-          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+          <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
         </is>
       </c>
       <c t="inlineStr" r="J39">
@@ -2230,7 +2230,7 @@
       </c>
       <c t="inlineStr" r="K39">
         <is>
-          <t xml:space="preserve">internal issues</t>
+          <t xml:space="preserve">texture black NP 38 not available another booking</t>
         </is>
       </c>
     </row>
@@ -2245,20 +2245,20 @@
       </c>
       <c t="inlineStr" r="C40">
         <is>
-          <t xml:space="preserve">Amal</t>
+          <t xml:space="preserve">isimal</t>
         </is>
       </c>
       <c r="D40" s="65">
-        <v>8921643216</v>
+        <v>9895447752</v>
       </c>
       <c t="inlineStr" r="E40">
         <is>
-          <t xml:space="preserve">18-12-2025</t>
+          <t xml:space="preserve">29-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F40">
         <is>
-          <t xml:space="preserve">Althaf A</t>
+          <t xml:space="preserve">SWAROOP S K</t>
         </is>
       </c>
       <c t="inlineStr" r="G40">
@@ -2273,7 +2273,7 @@
       </c>
       <c t="inlineStr" r="I40">
         <is>
-          <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
+          <t xml:space="preserve">Product Already Booked</t>
         </is>
       </c>
       <c t="inlineStr" r="J40">
@@ -2283,7 +2283,7 @@
       </c>
       <c t="inlineStr" r="K40">
         <is>
-          <t xml:space="preserve">texture black NP 38 not available another booking</t>
+          <t xml:space="preserve">prem black suit size required 36 set.</t>
         </is>
       </c>
     </row>
@@ -2298,20 +2298,20 @@
       </c>
       <c t="inlineStr" r="C41">
         <is>
-          <t xml:space="preserve">isimal</t>
+          <t xml:space="preserve">vishnu</t>
         </is>
       </c>
       <c r="D41" s="65">
-        <v>9895447752</v>
+        <v>9995931223</v>
       </c>
       <c t="inlineStr" r="E41">
         <is>
-          <t xml:space="preserve">29-12-2025</t>
+          <t xml:space="preserve">18-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F41">
         <is>
-          <t xml:space="preserve">SWAROOP S K</t>
+          <t xml:space="preserve">Mohamed Farseen C S</t>
         </is>
       </c>
       <c t="inlineStr" r="G41">
@@ -2326,7 +2326,7 @@
       </c>
       <c t="inlineStr" r="I41">
         <is>
-          <t xml:space="preserve">Product Already Booked</t>
+          <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
         </is>
       </c>
       <c t="inlineStr" r="J41">
@@ -2336,7 +2336,7 @@
       </c>
       <c t="inlineStr" r="K41">
         <is>
-          <t xml:space="preserve">prem black suit size required 36 set.</t>
+          <t xml:space="preserve">product not available in our store  already booked requirement for premium black shall</t>
         </is>
       </c>
     </row>
@@ -2351,11 +2351,11 @@
       </c>
       <c t="inlineStr" r="C42">
         <is>
-          <t xml:space="preserve">vishnu</t>
+          <t xml:space="preserve">mini</t>
         </is>
       </c>
       <c r="D42" s="65">
-        <v>9995931223</v>
+        <v>9497680722</v>
       </c>
       <c t="inlineStr" r="E42">
         <is>
@@ -2389,7 +2389,7 @@
       </c>
       <c t="inlineStr" r="K42">
         <is>
-          <t xml:space="preserve">product not available in our store  already booked requirement for premium black shall</t>
+          <t xml:space="preserve">black texture non premium</t>
         </is>
       </c>
     </row>
@@ -2404,11 +2404,11 @@
       </c>
       <c t="inlineStr" r="C43">
         <is>
-          <t xml:space="preserve">mini</t>
+          <t xml:space="preserve">Don jose</t>
         </is>
       </c>
       <c r="D43" s="65">
-        <v>9497680722</v>
+        <v>9895574884</v>
       </c>
       <c t="inlineStr" r="E43">
         <is>
@@ -2432,7 +2432,7 @@
       </c>
       <c t="inlineStr" r="I43">
         <is>
-          <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
+          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
         </is>
       </c>
       <c t="inlineStr" r="J43">
@@ -2442,7 +2442,7 @@
       </c>
       <c t="inlineStr" r="K43">
         <is>
-          <t xml:space="preserve">black texture non premium</t>
+          <t xml:space="preserve">customer required formal kids suite</t>
         </is>
       </c>
     </row>
@@ -2452,25 +2452,25 @@
       </c>
       <c t="inlineStr" r="B44">
         <is>
-          <t xml:space="preserve">18-12-2025</t>
+          <t xml:space="preserve">19-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C44">
         <is>
-          <t xml:space="preserve">Don jose</t>
+          <t xml:space="preserve">suthish</t>
         </is>
       </c>
       <c r="D44" s="65">
-        <v>9895574884</v>
+        <v>8606277718</v>
       </c>
       <c t="inlineStr" r="E44">
         <is>
-          <t xml:space="preserve">18-12-2025</t>
+          <t xml:space="preserve">10-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F44">
         <is>
-          <t xml:space="preserve">Mohamed Farseen C S</t>
+          <t xml:space="preserve">SWAROOP S K</t>
         </is>
       </c>
       <c t="inlineStr" r="G44">
@@ -2485,7 +2485,7 @@
       </c>
       <c t="inlineStr" r="I44">
         <is>
-          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
+          <t xml:space="preserve">Product Already Booked</t>
         </is>
       </c>
       <c t="inlineStr" r="J44">
@@ -2495,7 +2495,7 @@
       </c>
       <c t="inlineStr" r="K44">
         <is>
-          <t xml:space="preserve">customer required formal kids suite</t>
+          <t xml:space="preserve">blue shiny 42 size blazer</t>
         </is>
       </c>
     </row>
@@ -2510,20 +2510,20 @@
       </c>
       <c t="inlineStr" r="C45">
         <is>
-          <t xml:space="preserve">suthish</t>
+          <t xml:space="preserve">khaleel</t>
         </is>
       </c>
       <c r="D45" s="65">
-        <v>8606277718</v>
+        <v>8089977280</v>
       </c>
       <c t="inlineStr" r="E45">
         <is>
-          <t xml:space="preserve">10-01-2026</t>
+          <t xml:space="preserve">19-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F45">
         <is>
-          <t xml:space="preserve">SWAROOP S K</t>
+          <t xml:space="preserve">Mohamed Farseen C S</t>
         </is>
       </c>
       <c t="inlineStr" r="G45">
@@ -2533,12 +2533,12 @@
       </c>
       <c t="inlineStr" r="H45">
         <is>
-          <t xml:space="preserve">PRODUCT</t>
+          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
         </is>
       </c>
       <c t="inlineStr" r="I45">
         <is>
-          <t xml:space="preserve">Product Already Booked</t>
+          <t xml:space="preserve">BUDGET RESTRICTIONS</t>
         </is>
       </c>
       <c t="inlineStr" r="J45">
@@ -2548,7 +2548,7 @@
       </c>
       <c t="inlineStr" r="K45">
         <is>
-          <t xml:space="preserve">blue shiny 42 size blazer</t>
+          <t xml:space="preserve">bride restrictions</t>
         </is>
       </c>
     </row>
@@ -2563,20 +2563,20 @@
       </c>
       <c t="inlineStr" r="C46">
         <is>
-          <t xml:space="preserve">khaleel</t>
+          <t xml:space="preserve">Rizwan</t>
         </is>
       </c>
       <c r="D46" s="65">
-        <v>8089977280</v>
+        <v>8086945836</v>
       </c>
       <c t="inlineStr" r="E46">
         <is>
-          <t xml:space="preserve">19-12-2025</t>
+          <t xml:space="preserve">25-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F46">
         <is>
-          <t xml:space="preserve">Mohamed Farseen C S</t>
+          <t xml:space="preserve">Althaf A</t>
         </is>
       </c>
       <c t="inlineStr" r="G46">
@@ -2586,12 +2586,12 @@
       </c>
       <c t="inlineStr" r="H46">
         <is>
-          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
+          <t xml:space="preserve">PRODUCT</t>
         </is>
       </c>
       <c t="inlineStr" r="I46">
         <is>
-          <t xml:space="preserve">BUDGET RESTRICTIONS</t>
+          <t xml:space="preserve">REQUIRED DESIGN NOT AVAILABLE</t>
         </is>
       </c>
       <c t="inlineStr" r="J46">
@@ -2601,7 +2601,7 @@
       </c>
       <c t="inlineStr" r="K46">
         <is>
-          <t xml:space="preserve">bride restrictions</t>
+          <t xml:space="preserve">black with minimal print</t>
         </is>
       </c>
     </row>
@@ -2616,15 +2616,15 @@
       </c>
       <c t="inlineStr" r="C47">
         <is>
-          <t xml:space="preserve">Rizwan</t>
+          <t xml:space="preserve">Akshay</t>
         </is>
       </c>
       <c r="D47" s="65">
-        <v>8086945836</v>
+        <v>9400891463</v>
       </c>
       <c t="inlineStr" r="E47">
         <is>
-          <t xml:space="preserve">25-01-2026</t>
+          <t xml:space="preserve">09-02-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F47">
@@ -2639,12 +2639,12 @@
       </c>
       <c t="inlineStr" r="H47">
         <is>
-          <t xml:space="preserve">PRODUCT</t>
+          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
         </is>
       </c>
       <c t="inlineStr" r="I47">
         <is>
-          <t xml:space="preserve">REQUIRED DESIGN NOT AVAILABLE</t>
+          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
         </is>
       </c>
       <c t="inlineStr" r="J47">
@@ -2654,7 +2654,7 @@
       </c>
       <c t="inlineStr" r="K47">
         <is>
-          <t xml:space="preserve">black with minimal print</t>
+          <t xml:space="preserve">family disapproval</t>
         </is>
       </c>
     </row>
@@ -2664,25 +2664,25 @@
       </c>
       <c t="inlineStr" r="B48">
         <is>
-          <t xml:space="preserve">19-12-2025</t>
+          <t xml:space="preserve">20-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C48">
         <is>
-          <t xml:space="preserve">Akshay</t>
+          <t xml:space="preserve">musfar</t>
         </is>
       </c>
       <c r="D48" s="65">
-        <v>9400891463</v>
+        <v>9061752911</v>
       </c>
       <c t="inlineStr" r="E48">
         <is>
-          <t xml:space="preserve">09-02-2026</t>
+          <t xml:space="preserve">10-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F48">
         <is>
-          <t xml:space="preserve">Althaf A</t>
+          <t xml:space="preserve">SWAROOP S K</t>
         </is>
       </c>
       <c t="inlineStr" r="G48">
@@ -2707,7 +2707,7 @@
       </c>
       <c t="inlineStr" r="K48">
         <is>
-          <t xml:space="preserve">family disapproval</t>
+          <t xml:space="preserve">.</t>
         </is>
       </c>
     </row>
@@ -2722,20 +2722,20 @@
       </c>
       <c t="inlineStr" r="C49">
         <is>
-          <t xml:space="preserve">musfar</t>
+          <t xml:space="preserve">Zayan</t>
         </is>
       </c>
       <c r="D49" s="65">
-        <v>9061752911</v>
+        <v>9846858838</v>
       </c>
       <c t="inlineStr" r="E49">
         <is>
-          <t xml:space="preserve">10-01-2026</t>
+          <t xml:space="preserve">21-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F49">
         <is>
-          <t xml:space="preserve">SWAROOP S K</t>
+          <t xml:space="preserve">Binu Augustine</t>
         </is>
       </c>
       <c t="inlineStr" r="G49">
@@ -2745,12 +2745,12 @@
       </c>
       <c t="inlineStr" r="H49">
         <is>
-          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
+          <t xml:space="preserve">PRODUCT</t>
         </is>
       </c>
       <c t="inlineStr" r="I49">
         <is>
-          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
+          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
         </is>
       </c>
       <c t="inlineStr" r="J49">
@@ -2760,7 +2760,7 @@
       </c>
       <c t="inlineStr" r="K49">
         <is>
-          <t xml:space="preserve">.</t>
+          <t xml:space="preserve">function is tommorow</t>
         </is>
       </c>
     </row>
@@ -2775,20 +2775,20 @@
       </c>
       <c t="inlineStr" r="C50">
         <is>
-          <t xml:space="preserve">Zayan</t>
+          <t xml:space="preserve">safeer</t>
         </is>
       </c>
       <c r="D50" s="65">
-        <v>9846858838</v>
+        <v>8606123654</v>
       </c>
       <c t="inlineStr" r="E50">
         <is>
-          <t xml:space="preserve">21-12-2025</t>
+          <t xml:space="preserve">23-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F50">
         <is>
-          <t xml:space="preserve">Binu Augustine</t>
+          <t xml:space="preserve">SWAROOP S K</t>
         </is>
       </c>
       <c t="inlineStr" r="G50">
@@ -2798,12 +2798,12 @@
       </c>
       <c t="inlineStr" r="H50">
         <is>
-          <t xml:space="preserve">PRODUCT</t>
+          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
         </is>
       </c>
       <c t="inlineStr" r="I50">
         <is>
-          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
+          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
         </is>
       </c>
       <c t="inlineStr" r="J50">
@@ -2813,7 +2813,7 @@
       </c>
       <c t="inlineStr" r="K50">
         <is>
-          <t xml:space="preserve">function is tommorow</t>
+          <t xml:space="preserve">.</t>
         </is>
       </c>
     </row>
@@ -2828,20 +2828,20 @@
       </c>
       <c t="inlineStr" r="C51">
         <is>
-          <t xml:space="preserve">safeer</t>
+          <t xml:space="preserve">keba paul</t>
         </is>
       </c>
       <c r="D51" s="65">
-        <v>8606123654</v>
+        <v>8590118941</v>
       </c>
       <c t="inlineStr" r="E51">
         <is>
-          <t xml:space="preserve">23-12-2025</t>
+          <t xml:space="preserve">26-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F51">
         <is>
-          <t xml:space="preserve">SWAROOP S K</t>
+          <t xml:space="preserve">ABIN KRISHNA S</t>
         </is>
       </c>
       <c t="inlineStr" r="G51">
@@ -2851,12 +2851,12 @@
       </c>
       <c t="inlineStr" r="H51">
         <is>
-          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
+          <t xml:space="preserve">ENQUIRY</t>
         </is>
       </c>
       <c t="inlineStr" r="I51">
         <is>
-          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
         </is>
       </c>
       <c t="inlineStr" r="J51">
@@ -2866,7 +2866,7 @@
       </c>
       <c t="inlineStr" r="K51">
         <is>
-          <t xml:space="preserve">.</t>
+          <t xml:space="preserve">size not availabe</t>
         </is>
       </c>
     </row>
@@ -2881,15 +2881,15 @@
       </c>
       <c t="inlineStr" r="C52">
         <is>
-          <t xml:space="preserve">keba paul</t>
+          <t xml:space="preserve">linu</t>
         </is>
       </c>
       <c r="D52" s="65">
-        <v>8590118941</v>
+        <v>7293168811</v>
       </c>
       <c t="inlineStr" r="E52">
         <is>
-          <t xml:space="preserve">26-12-2025</t>
+          <t xml:space="preserve">27-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F52">
@@ -2909,7 +2909,7 @@
       </c>
       <c t="inlineStr" r="I52">
         <is>
-          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+          <t xml:space="preserve">Enquiry for Relative/Friend</t>
         </is>
       </c>
       <c t="inlineStr" r="J52">
@@ -2919,7 +2919,7 @@
       </c>
       <c t="inlineStr" r="K52">
         <is>
-          <t xml:space="preserve">size not availabe</t>
+          <t xml:space="preserve">enquiry</t>
         </is>
       </c>
     </row>
@@ -2934,15 +2934,15 @@
       </c>
       <c t="inlineStr" r="C53">
         <is>
-          <t xml:space="preserve">linu</t>
+          <t xml:space="preserve">indrajith</t>
         </is>
       </c>
       <c r="D53" s="65">
-        <v>7293168811</v>
+        <v>7012239991</v>
       </c>
       <c t="inlineStr" r="E53">
         <is>
-          <t xml:space="preserve">27-12-2025</t>
+          <t xml:space="preserve">06-05-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F53">
@@ -2972,7 +2972,7 @@
       </c>
       <c t="inlineStr" r="K53">
         <is>
-          <t xml:space="preserve">enquiry</t>
+          <t xml:space="preserve">for enquiry</t>
         </is>
       </c>
     </row>
@@ -2982,25 +2982,25 @@
       </c>
       <c t="inlineStr" r="B54">
         <is>
-          <t xml:space="preserve">20-12-2025</t>
+          <t xml:space="preserve">21-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C54">
         <is>
-          <t xml:space="preserve">indrajith</t>
+          <t xml:space="preserve">Anoop</t>
         </is>
       </c>
       <c r="D54" s="65">
-        <v>7012239991</v>
+        <v>7974143534</v>
       </c>
       <c t="inlineStr" r="E54">
         <is>
-          <t xml:space="preserve">06-05-2026</t>
+          <t xml:space="preserve">04-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F54">
         <is>
-          <t xml:space="preserve">ABIN KRISHNA S</t>
+          <t xml:space="preserve">SWAROOP S K</t>
         </is>
       </c>
       <c t="inlineStr" r="G54">
@@ -3010,12 +3010,12 @@
       </c>
       <c t="inlineStr" r="H54">
         <is>
-          <t xml:space="preserve">ENQUIRY</t>
+          <t xml:space="preserve">PRODUCT</t>
         </is>
       </c>
       <c t="inlineStr" r="I54">
         <is>
-          <t xml:space="preserve">Enquiry for Relative/Friend</t>
+          <t xml:space="preserve">Product Already Booked</t>
         </is>
       </c>
       <c t="inlineStr" r="J54">
@@ -3025,7 +3025,7 @@
       </c>
       <c t="inlineStr" r="K54">
         <is>
-          <t xml:space="preserve">for enquiry</t>
+          <t xml:space="preserve">coustomer is conformed product but product is booked. Product - Cream open B/G</t>
         </is>
       </c>
     </row>
@@ -3040,20 +3040,20 @@
       </c>
       <c t="inlineStr" r="C55">
         <is>
-          <t xml:space="preserve">Anoop</t>
+          <t xml:space="preserve">binoy</t>
         </is>
       </c>
       <c r="D55" s="65">
-        <v>7974143534</v>
+        <v>9061762422</v>
       </c>
       <c t="inlineStr" r="E55">
         <is>
-          <t xml:space="preserve">04-01-2026</t>
+          <t xml:space="preserve">21-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F55">
         <is>
-          <t xml:space="preserve">SWAROOP S K</t>
+          <t xml:space="preserve">Mohamed Farseen C S</t>
         </is>
       </c>
       <c t="inlineStr" r="G55">
@@ -3063,12 +3063,12 @@
       </c>
       <c t="inlineStr" r="H55">
         <is>
-          <t xml:space="preserve">PRODUCT</t>
+          <t xml:space="preserve">ENQUIRY</t>
         </is>
       </c>
       <c t="inlineStr" r="I55">
         <is>
-          <t xml:space="preserve">Product Already Booked</t>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
         </is>
       </c>
       <c t="inlineStr" r="J55">
@@ -3078,7 +3078,7 @@
       </c>
       <c t="inlineStr" r="K55">
         <is>
-          <t xml:space="preserve">coustomer is conformed product but product is booked. Product - Cream open B/G</t>
+          <t xml:space="preserve">enquiry for open bengala customer not satisfied</t>
         </is>
       </c>
     </row>
@@ -3093,11 +3093,11 @@
       </c>
       <c t="inlineStr" r="C56">
         <is>
-          <t xml:space="preserve">binoy</t>
+          <t xml:space="preserve">pranav</t>
         </is>
       </c>
       <c r="D56" s="65">
-        <v>9061762422</v>
+        <v>7012395349</v>
       </c>
       <c t="inlineStr" r="E56">
         <is>
@@ -3116,12 +3116,12 @@
       </c>
       <c t="inlineStr" r="H56">
         <is>
-          <t xml:space="preserve">ENQUIRY</t>
+          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
         </is>
       </c>
       <c t="inlineStr" r="I56">
         <is>
-          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
         </is>
       </c>
       <c t="inlineStr" r="J56">
@@ -3131,7 +3131,7 @@
       </c>
       <c t="inlineStr" r="K56">
         <is>
-          <t xml:space="preserve">enquiry for open bengala customer not satisfied</t>
+          <t xml:space="preserve">required model not available</t>
         </is>
       </c>
     </row>
@@ -3146,20 +3146,20 @@
       </c>
       <c t="inlineStr" r="C57">
         <is>
-          <t xml:space="preserve">pranav</t>
+          <t xml:space="preserve">vishnu</t>
         </is>
       </c>
       <c r="D57" s="65">
-        <v>7012395349</v>
+        <v>8129349296</v>
       </c>
       <c t="inlineStr" r="E57">
         <is>
-          <t xml:space="preserve">21-12-2025</t>
+          <t xml:space="preserve">29-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F57">
         <is>
-          <t xml:space="preserve">Mohamed Farseen C S</t>
+          <t xml:space="preserve">SWAROOP S K</t>
         </is>
       </c>
       <c t="inlineStr" r="G57">
@@ -3184,7 +3184,7 @@
       </c>
       <c t="inlineStr" r="K57">
         <is>
-          <t xml:space="preserve">required model not available</t>
+          <t xml:space="preserve">Family problem Will be come</t>
         </is>
       </c>
     </row>
@@ -3199,20 +3199,20 @@
       </c>
       <c t="inlineStr" r="C58">
         <is>
-          <t xml:space="preserve">vishnu</t>
+          <t xml:space="preserve">thanveer</t>
         </is>
       </c>
       <c r="D58" s="65">
-        <v>8129349296</v>
+        <v>9947874867</v>
       </c>
       <c t="inlineStr" r="E58">
         <is>
-          <t xml:space="preserve">29-12-2025</t>
+          <t xml:space="preserve">07-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F58">
         <is>
-          <t xml:space="preserve">SWAROOP S K</t>
+          <t xml:space="preserve">Binu Augustine</t>
         </is>
       </c>
       <c t="inlineStr" r="G58">
@@ -3222,12 +3222,12 @@
       </c>
       <c t="inlineStr" r="H58">
         <is>
-          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
+          <t xml:space="preserve">ENQUIRY</t>
         </is>
       </c>
       <c t="inlineStr" r="I58">
         <is>
-          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
         </is>
       </c>
       <c t="inlineStr" r="J58">
@@ -3237,7 +3237,7 @@
       </c>
       <c t="inlineStr" r="K58">
         <is>
-          <t xml:space="preserve">Family problem Will be come</t>
+          <t xml:space="preserve">.</t>
         </is>
       </c>
     </row>
@@ -3252,15 +3252,15 @@
       </c>
       <c t="inlineStr" r="C59">
         <is>
-          <t xml:space="preserve">thanveer</t>
+          <t xml:space="preserve">tom</t>
         </is>
       </c>
       <c r="D59" s="65">
-        <v>9947874867</v>
+        <v>8281692848</v>
       </c>
       <c t="inlineStr" r="E59">
         <is>
-          <t xml:space="preserve">07-01-2026</t>
+          <t xml:space="preserve">03-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F59">
@@ -3300,25 +3300,25 @@
       </c>
       <c t="inlineStr" r="B60">
         <is>
-          <t xml:space="preserve">21-12-2025</t>
+          <t xml:space="preserve">22-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C60">
         <is>
-          <t xml:space="preserve">tom</t>
+          <t xml:space="preserve">Madhav</t>
         </is>
       </c>
       <c r="D60" s="65">
-        <v>8281692848</v>
+        <v>6282156345</v>
       </c>
       <c t="inlineStr" r="E60">
         <is>
-          <t xml:space="preserve">03-01-2026</t>
+          <t xml:space="preserve">28-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F60">
         <is>
-          <t xml:space="preserve">Binu Augustine</t>
+          <t xml:space="preserve">Althaf A</t>
         </is>
       </c>
       <c t="inlineStr" r="G60">
@@ -3328,12 +3328,12 @@
       </c>
       <c t="inlineStr" r="H60">
         <is>
-          <t xml:space="preserve">ENQUIRY</t>
+          <t xml:space="preserve">SIZE NOT SUITABLE</t>
         </is>
       </c>
       <c t="inlineStr" r="I60">
         <is>
-          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+          <t xml:space="preserve">SIZE TOO SMALL</t>
         </is>
       </c>
       <c t="inlineStr" r="J60">
@@ -3343,7 +3343,7 @@
       </c>
       <c t="inlineStr" r="K60">
         <is>
-          <t xml:space="preserve">.</t>
+          <t xml:space="preserve">black size 38 required</t>
         </is>
       </c>
     </row>
@@ -3358,15 +3358,15 @@
       </c>
       <c t="inlineStr" r="C61">
         <is>
-          <t xml:space="preserve">Madhav</t>
+          <t xml:space="preserve">Tony</t>
         </is>
       </c>
       <c r="D61" s="65">
-        <v>6282156345</v>
+        <v>8075613454</v>
       </c>
       <c t="inlineStr" r="E61">
         <is>
-          <t xml:space="preserve">28-12-2025</t>
+          <t xml:space="preserve">14-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F61">
@@ -3381,12 +3381,12 @@
       </c>
       <c t="inlineStr" r="H61">
         <is>
-          <t xml:space="preserve">SIZE NOT SUITABLE</t>
+          <t xml:space="preserve">PRODUCT</t>
         </is>
       </c>
       <c t="inlineStr" r="I61">
         <is>
-          <t xml:space="preserve">SIZE TOO SMALL</t>
+          <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
         </is>
       </c>
       <c t="inlineStr" r="J61">
@@ -3396,7 +3396,7 @@
       </c>
       <c t="inlineStr" r="K61">
         <is>
-          <t xml:space="preserve">black size 38 required</t>
+          <t xml:space="preserve">customer required date product is not available</t>
         </is>
       </c>
     </row>
@@ -3411,20 +3411,20 @@
       </c>
       <c t="inlineStr" r="C62">
         <is>
-          <t xml:space="preserve">Tony</t>
+          <t xml:space="preserve">noyal</t>
         </is>
       </c>
       <c r="D62" s="65">
-        <v>8075613454</v>
+        <v>7034875397</v>
       </c>
       <c t="inlineStr" r="E62">
         <is>
-          <t xml:space="preserve">14-01-2026</t>
+          <t xml:space="preserve">10-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F62">
         <is>
-          <t xml:space="preserve">Althaf A</t>
+          <t xml:space="preserve">AKSHAYDAS.M</t>
         </is>
       </c>
       <c t="inlineStr" r="G62">
@@ -3434,12 +3434,12 @@
       </c>
       <c t="inlineStr" r="H62">
         <is>
-          <t xml:space="preserve">PRODUCT</t>
+          <t xml:space="preserve">SIZE NOT SUITABLE</t>
         </is>
       </c>
       <c t="inlineStr" r="I62">
         <is>
-          <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
+          <t xml:space="preserve">SIZE TOO SMALL</t>
         </is>
       </c>
       <c t="inlineStr" r="J62">
@@ -3449,7 +3449,7 @@
       </c>
       <c t="inlineStr" r="K62">
         <is>
-          <t xml:space="preserve">customer required date product is not available</t>
+          <t xml:space="preserve">..</t>
         </is>
       </c>
     </row>
@@ -3464,15 +3464,15 @@
       </c>
       <c t="inlineStr" r="C63">
         <is>
-          <t xml:space="preserve">noyal</t>
+          <t xml:space="preserve">shahul</t>
         </is>
       </c>
       <c r="D63" s="65">
-        <v>7034875397</v>
+        <v>8921029730</v>
       </c>
       <c t="inlineStr" r="E63">
         <is>
-          <t xml:space="preserve">10-01-2026</t>
+          <t xml:space="preserve">18-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F63">
@@ -3487,12 +3487,12 @@
       </c>
       <c t="inlineStr" r="H63">
         <is>
-          <t xml:space="preserve">SIZE NOT SUITABLE</t>
+          <t xml:space="preserve">PRODUCT</t>
         </is>
       </c>
       <c t="inlineStr" r="I63">
         <is>
-          <t xml:space="preserve">SIZE TOO SMALL</t>
+          <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
         </is>
       </c>
       <c t="inlineStr" r="J63">
@@ -3512,25 +3512,25 @@
       </c>
       <c t="inlineStr" r="B64">
         <is>
-          <t xml:space="preserve">22-12-2025</t>
+          <t xml:space="preserve">23-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C64">
         <is>
-          <t xml:space="preserve">shahul</t>
+          <t xml:space="preserve">Anandu</t>
         </is>
       </c>
       <c r="D64" s="65">
-        <v>8921029730</v>
+        <v>9526656855</v>
       </c>
       <c t="inlineStr" r="E64">
         <is>
-          <t xml:space="preserve">18-01-2026</t>
+          <t xml:space="preserve">08-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F64">
         <is>
-          <t xml:space="preserve">AKSHAYDAS.M</t>
+          <t xml:space="preserve">Althaf A</t>
         </is>
       </c>
       <c t="inlineStr" r="G64">
@@ -3540,12 +3540,12 @@
       </c>
       <c t="inlineStr" r="H64">
         <is>
-          <t xml:space="preserve">PRODUCT</t>
+          <t xml:space="preserve">SIZE NOT SUITABLE</t>
         </is>
       </c>
       <c t="inlineStr" r="I64">
         <is>
-          <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
+          <t xml:space="preserve">SIZE TOO SMALL</t>
         </is>
       </c>
       <c t="inlineStr" r="J64">
@@ -3555,7 +3555,7 @@
       </c>
       <c t="inlineStr" r="K64">
         <is>
-          <t xml:space="preserve">..</t>
+          <t xml:space="preserve">required 46 premium suit</t>
         </is>
       </c>
     </row>
@@ -3565,20 +3565,20 @@
       </c>
       <c t="inlineStr" r="B65">
         <is>
-          <t xml:space="preserve">23-12-2025</t>
+          <t xml:space="preserve">24-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C65">
         <is>
-          <t xml:space="preserve">Anandu</t>
+          <t xml:space="preserve">Athul</t>
         </is>
       </c>
       <c r="D65" s="65">
-        <v>9526656855</v>
+        <v>9744852238</v>
       </c>
       <c t="inlineStr" r="E65">
         <is>
-          <t xml:space="preserve">08-01-2026</t>
+          <t xml:space="preserve">07-02-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F65">
@@ -3593,12 +3593,12 @@
       </c>
       <c t="inlineStr" r="H65">
         <is>
-          <t xml:space="preserve">SIZE NOT SUITABLE</t>
+          <t xml:space="preserve">PRODUCT</t>
         </is>
       </c>
       <c t="inlineStr" r="I65">
         <is>
-          <t xml:space="preserve">SIZE TOO SMALL</t>
+          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
         </is>
       </c>
       <c t="inlineStr" r="J65">
@@ -3608,7 +3608,7 @@
       </c>
       <c t="inlineStr" r="K65">
         <is>
-          <t xml:space="preserve">required 46 premium suit</t>
+          <t xml:space="preserve">required design and color not available ( black indowestern with stone work )</t>
         </is>
       </c>
     </row>
@@ -3618,25 +3618,25 @@
       </c>
       <c t="inlineStr" r="B66">
         <is>
-          <t xml:space="preserve">24-12-2025</t>
+          <t xml:space="preserve">25-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C66">
         <is>
-          <t xml:space="preserve">Athul</t>
+          <t xml:space="preserve">althaf</t>
         </is>
       </c>
       <c r="D66" s="65">
-        <v>9744852238</v>
+        <v>9656287663</v>
       </c>
       <c t="inlineStr" r="E66">
         <is>
-          <t xml:space="preserve">07-02-2026</t>
+          <t xml:space="preserve">11-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F66">
         <is>
-          <t xml:space="preserve">Althaf A</t>
+          <t xml:space="preserve">ABIN KRISHNA S</t>
         </is>
       </c>
       <c t="inlineStr" r="G66">
@@ -3646,12 +3646,12 @@
       </c>
       <c t="inlineStr" r="H66">
         <is>
-          <t xml:space="preserve">PRODUCT</t>
+          <t xml:space="preserve">ENQUIRY</t>
         </is>
       </c>
       <c t="inlineStr" r="I66">
         <is>
-          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
+          <t xml:space="preserve">Enquiry for Relative/Friend</t>
         </is>
       </c>
       <c t="inlineStr" r="J66">
@@ -3661,7 +3661,7 @@
       </c>
       <c t="inlineStr" r="K66">
         <is>
-          <t xml:space="preserve">required design and color not available ( black indowestern with stone work )</t>
+          <t xml:space="preserve">enquiry</t>
         </is>
       </c>
     </row>
@@ -3671,50 +3671,580 @@
       </c>
       <c t="inlineStr" r="B67">
         <is>
-          <t xml:space="preserve">25-12-2025</t>
+          <t xml:space="preserve">27-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C67">
         <is>
-          <t xml:space="preserve">althaf</t>
+          <t xml:space="preserve">Nibin</t>
         </is>
       </c>
       <c r="D67" s="65">
-        <v>9656287663</v>
+        <v>8891681034</v>
       </c>
       <c t="inlineStr" r="E67">
         <is>
+          <t xml:space="preserve">09-02-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F67">
+        <is>
+          <t xml:space="preserve">SWAROOP S K</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G67">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H67">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I67">
+        <is>
+          <t xml:space="preserve">Product Already Booked</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J67">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K67">
+        <is>
+          <t xml:space="preserve">ULTRA LUXURY INDOWESTERN 40 SIZE</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="65">
+        <v>66</v>
+      </c>
+      <c t="inlineStr" r="B68">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C68">
+        <is>
+          <t xml:space="preserve">anosh</t>
+        </is>
+      </c>
+      <c r="D68" s="65">
+        <v>7560956201</v>
+      </c>
+      <c t="inlineStr" r="E68">
+        <is>
+          <t xml:space="preserve">05-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F68">
+        <is>
+          <t xml:space="preserve">ABIN KRISHNA S</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G68">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H68">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I68">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J68">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K68">
+        <is>
+          <t xml:space="preserve">enquiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="65">
+        <v>67</v>
+      </c>
+      <c t="inlineStr" r="B69">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C69">
+        <is>
+          <t xml:space="preserve">aslin</t>
+        </is>
+      </c>
+      <c r="D69" s="65">
+        <v>9747617657</v>
+      </c>
+      <c t="inlineStr" r="E69">
+        <is>
+          <t xml:space="preserve">12-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F69">
+        <is>
+          <t xml:space="preserve">Binu Augustine</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G69">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H69">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I69">
+        <is>
+          <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J69">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K69">
+        <is>
+          <t xml:space="preserve">.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="65">
+        <v>68</v>
+      </c>
+      <c t="inlineStr" r="B70">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C70">
+        <is>
+          <t xml:space="preserve">abhilash</t>
+        </is>
+      </c>
+      <c r="D70" s="65">
+        <v>9946615151</v>
+      </c>
+      <c t="inlineStr" r="E70">
+        <is>
+          <t xml:space="preserve">14-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F70">
+        <is>
+          <t xml:space="preserve">Binu Augustine</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G70">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H70">
+        <is>
+          <t xml:space="preserve">SIZE NOT SUITABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I70">
+        <is>
+          <t xml:space="preserve">SIZE TOO LARGE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J70">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K70">
+        <is>
+          <t xml:space="preserve">will come mid days of week</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="65">
+        <v>69</v>
+      </c>
+      <c t="inlineStr" r="B71">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C71">
+        <is>
+          <t xml:space="preserve">Athul</t>
+        </is>
+      </c>
+      <c r="D71" s="65">
+        <v>9995707235</v>
+      </c>
+      <c t="inlineStr" r="E71">
+        <is>
           <t xml:space="preserve">11-01-2026</t>
         </is>
       </c>
-      <c t="inlineStr" r="F67">
-        <is>
-          <t xml:space="preserve">ABIN KRISHNA S</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="G67">
-        <is>
-          <t xml:space="preserve">Loss</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="H67">
+      <c t="inlineStr" r="F71">
+        <is>
+          <t xml:space="preserve">Althaf A</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G71">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H71">
         <is>
           <t xml:space="preserve">ENQUIRY</t>
         </is>
       </c>
-      <c t="inlineStr" r="I67">
+      <c t="inlineStr" r="I71">
         <is>
           <t xml:space="preserve">Enquiry for Relative/Friend</t>
         </is>
       </c>
-      <c t="inlineStr" r="J67">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="K67">
-        <is>
-          <t xml:space="preserve">enquiry</t>
+      <c t="inlineStr" r="J71">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K71">
+        <is>
+          <t xml:space="preserve">He came for enquiry for his friend</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="65">
+        <v>70</v>
+      </c>
+      <c t="inlineStr" r="B72">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C72">
+        <is>
+          <t xml:space="preserve">josh</t>
+        </is>
+      </c>
+      <c r="D72" s="65">
+        <v>9895656017</v>
+      </c>
+      <c t="inlineStr" r="E72">
+        <is>
+          <t xml:space="preserve">22-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F72">
+        <is>
+          <t xml:space="preserve">Binu Augustine</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G72">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H72">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I72">
+        <is>
+          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J72">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K72">
+        <is>
+          <t xml:space="preserve">royal blue texido suit need, recommended to mg road</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="65">
+        <v>71</v>
+      </c>
+      <c t="inlineStr" r="B73">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C73">
+        <is>
+          <t xml:space="preserve">jeesmon</t>
+        </is>
+      </c>
+      <c r="D73" s="65">
+        <v>8089547507</v>
+      </c>
+      <c t="inlineStr" r="E73">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F73">
+        <is>
+          <t xml:space="preserve">Nithin binoy</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G73">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H73">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I73">
+        <is>
+          <t xml:space="preserve">Enquiry for Relative/Friend</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J73">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K73">
+        <is>
+          <t xml:space="preserve">los</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="65">
+        <v>72</v>
+      </c>
+      <c t="inlineStr" r="B74">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C74">
+        <is>
+          <t xml:space="preserve">niyas</t>
+        </is>
+      </c>
+      <c r="D74" s="65">
+        <v>7736777624</v>
+      </c>
+      <c t="inlineStr" r="E74">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F74">
+        <is>
+          <t xml:space="preserve">Nithin binoy</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G74">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H74">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I74">
+        <is>
+          <t xml:space="preserve">REQUIRED DESIGN NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J74">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K74">
+        <is>
+          <t xml:space="preserve">bengala white premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="65">
+        <v>73</v>
+      </c>
+      <c t="inlineStr" r="B75">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C75">
+        <is>
+          <t xml:space="preserve">thomas</t>
+        </is>
+      </c>
+      <c r="D75" s="65">
+        <v>8111919282</v>
+      </c>
+      <c t="inlineStr" r="E75">
+        <is>
+          <t xml:space="preserve">04-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F75">
+        <is>
+          <t xml:space="preserve">AKSHAYDAS.M</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G75">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H75">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I75">
+        <is>
+          <t xml:space="preserve">Product Already Booked</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J75">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K75">
+        <is>
+          <t xml:space="preserve">..</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="65">
+        <v>74</v>
+      </c>
+      <c t="inlineStr" r="B76">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C76">
+        <is>
+          <t xml:space="preserve">salvin</t>
+        </is>
+      </c>
+      <c r="D76" s="65">
+        <v>9995920408</v>
+      </c>
+      <c t="inlineStr" r="E76">
+        <is>
+          <t xml:space="preserve">05-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F76">
+        <is>
+          <t xml:space="preserve">JISHNU.R</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G76">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H76">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I76">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J76">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K76">
+        <is>
+          <t xml:space="preserve">we will come family</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="65">
+        <v>75</v>
+      </c>
+      <c t="inlineStr" r="B77">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C77">
+        <is>
+          <t xml:space="preserve">Renchu</t>
+        </is>
+      </c>
+      <c r="D77" s="65">
+        <v>8075936488</v>
+      </c>
+      <c t="inlineStr" r="E77">
+        <is>
+          <t xml:space="preserve">19-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F77">
+        <is>
+          <t xml:space="preserve">SWAROOP S K</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G77">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H77">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I77">
+        <is>
+          <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J77">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K77">
+        <is>
+          <t xml:space="preserve">Product is rentout tomorrow will be coming product</t>
         </is>
       </c>
     </row>
